--- a/食譜.xlsx
+++ b/食譜.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\skyan\OneDrive\桌面\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26BCB05D-B805-45C9-8AFF-53077781B18A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ECC2CF9-8086-40D5-AD79-E47EE079A851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{D3CD4B5A-BC5A-4F70-9177-788540974920}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D3CD4B5A-BC5A-4F70-9177-788540974920}"/>
   </bookViews>
   <sheets>
     <sheet name="菜式清單" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
     <author>Claude</author>
   </authors>
   <commentList>
-    <comment ref="C25" authorId="0" shapeId="0" xr:uid="{9C86073D-2677-417A-AB08-D321EF476175}">
+    <comment ref="D25" authorId="0" shapeId="0" xr:uid="{9C86073D-2677-417A-AB08-D321EF476175}">
       <text>
         <r>
           <rPr>
@@ -63,7 +63,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C27" authorId="0" shapeId="0" xr:uid="{A12E4064-7AC7-44CA-B38A-D3C80F88A937}">
+    <comment ref="D27" authorId="0" shapeId="0" xr:uid="{A12E4064-7AC7-44CA-B38A-D3C80F88A937}">
       <text>
         <r>
           <rPr>
@@ -78,7 +78,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C37" authorId="0" shapeId="0" xr:uid="{6519F562-A210-4DD1-84AC-E4ADDCB099F3}">
+    <comment ref="D37" authorId="0" shapeId="0" xr:uid="{6519F562-A210-4DD1-84AC-E4ADDCB099F3}">
       <text>
         <r>
           <rPr>
@@ -93,7 +93,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C39" authorId="0" shapeId="0" xr:uid="{10BEF367-7427-40D8-AE86-2AD0D973BB24}">
+    <comment ref="D39" authorId="0" shapeId="0" xr:uid="{10BEF367-7427-40D8-AE86-2AD0D973BB24}">
       <text>
         <r>
           <rPr>
@@ -108,7 +108,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C48" authorId="0" shapeId="0" xr:uid="{C7FD163B-885B-4706-80A0-EB69B0F9D8A6}">
+    <comment ref="D48" authorId="0" shapeId="0" xr:uid="{C7FD163B-885B-4706-80A0-EB69B0F9D8A6}">
       <text>
         <r>
           <rPr>
@@ -123,7 +123,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C50" authorId="0" shapeId="0" xr:uid="{57F2032D-C667-4AC0-AAE1-83F208426282}">
+    <comment ref="D50" authorId="0" shapeId="0" xr:uid="{57F2032D-C667-4AC0-AAE1-83F208426282}">
       <text>
         <r>
           <rPr>
@@ -142,30 +142,8 @@
 </comments>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3321" uniqueCount="870">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3373" uniqueCount="888">
   <si>
     <r>
       <rPr>
@@ -5634,6 +5612,75 @@
   </si>
   <si>
     <t>Cat ears Fugus</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step_EN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step_FIL</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step_ID</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>菜名</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提香用</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可省略</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>依序將高麗菜與豬五花薄片均勻鋪在鍋中, 淋紹興酒(可省略)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>藝上鍋蓋,以小火燜煮7-10分鐘, 至肉片熟透</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>將前四項調味料與蒜末一起混合均勻,淋在肉片上.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>薄切梅花豬肉片</t>
+  </si>
+  <si>
+    <t>薄切梅花豬肉片</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>板豆腐</t>
+  </si>
+  <si>
+    <t>板豆腐</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>塊</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>味醂</t>
+  </si>
+  <si>
+    <t>將豆腐條包進肉片後捲起</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>以少許油熱鍋後,將肉接縫處朝下用中小火煎, 若有剩的豆腐也可一起放入鍋中煎</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>待肉每一面都煎熟後, 淋上調味料, 此時需不時翻動肉讓醬汁均勻吸附, 等醬汁變濃稠,肉捲上色入味後,即完成</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -5641,7 +5688,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -5741,8 +5788,16 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5779,8 +5834,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -5808,13 +5869,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5875,18 +5949,89 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="35">
+  <dxfs count="40">
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -5916,25 +6061,14 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
         <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -5963,24 +6097,11 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -5995,11 +6116,15 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -6013,7 +6138,11 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -6024,6 +6153,25 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -6394,11 +6542,49 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -6430,11 +6616,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -6448,25 +6630,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
+        <b/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -6496,133 +6660,90 @@
 </styleSheet>
 </file>
 
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>9</v>
-    <v>1</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="subType" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DE57552F-D026-4EAF-97C3-52DD25EAFC9C}" name="表格1" displayName="表格1" ref="A3:N261" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DE57552F-D026-4EAF-97C3-52DD25EAFC9C}" name="表格1" displayName="表格1" ref="A3:N261" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31">
   <autoFilter ref="A3:N261" xr:uid="{DE57552F-D026-4EAF-97C3-52DD25EAFC9C}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:J97">
     <sortCondition ref="B3:B97"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="3" xr3:uid="{9F4CF7F5-2A93-4AB2-B6A9-ADD9938F5AA8}" name="ID" dataDxfId="27"/>
-    <tableColumn id="1" xr3:uid="{2F06CBD1-1A4C-4DC5-BCE4-F3C9A79DC3E9}" name="Cuisine" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{7EC406AA-A572-4016-9E5B-51B700036584}" name="Diet" dataDxfId="25"/>
-    <tableColumn id="9" xr3:uid="{D9CE8FCA-CFAD-4F3F-8F01-0C4484946BEA}" name="Dish" dataDxfId="24"/>
-    <tableColumn id="10" xr3:uid="{673F4675-BEEE-412A-A6CB-20E6D1E799D8}" name="Breakfast" dataDxfId="23"/>
-    <tableColumn id="12" xr3:uid="{D37C5B0D-12C6-4CB3-BB80-08C12E6E49B6}" name="Lunch" dataDxfId="22"/>
-    <tableColumn id="13" xr3:uid="{E25F656B-1F18-455E-87D7-5C9D9B0097A5}" name="Dinner" dataDxfId="21"/>
-    <tableColumn id="17" xr3:uid="{BA985DFD-A4E6-404F-8823-002672B31C18}" name="Light Meal" dataDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{A034FE6E-ED0A-4EFB-8D1C-030735AED3C9}" name="Main Protein" dataDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{AA4E79D0-DAC8-43FF-A045-39E8C3C9F5CD}" name="Dish Role" dataDxfId="18"/>
-    <tableColumn id="15" xr3:uid="{3C0D36C0-00D9-469A-9A08-C9CBF82D88AE}" name="Taste" dataDxfId="17"/>
-    <tableColumn id="7" xr3:uid="{23809AC8-474B-40F8-84CF-2D42F7BE1C9D}" name="Expire(day)" dataDxfId="16"/>
-    <tableColumn id="8" xr3:uid="{FA20BD4E-AF4A-4273-8F29-845E2CF561A3}" name="Season" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{63A3F435-6F07-4F3F-B146-E824E495A1E4}" name="Credit to" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{9F4CF7F5-2A93-4AB2-B6A9-ADD9938F5AA8}" name="ID" dataDxfId="30"/>
+    <tableColumn id="1" xr3:uid="{2F06CBD1-1A4C-4DC5-BCE4-F3C9A79DC3E9}" name="Cuisine" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{7EC406AA-A572-4016-9E5B-51B700036584}" name="Diet" dataDxfId="28"/>
+    <tableColumn id="9" xr3:uid="{D9CE8FCA-CFAD-4F3F-8F01-0C4484946BEA}" name="Dish" dataDxfId="27"/>
+    <tableColumn id="10" xr3:uid="{673F4675-BEEE-412A-A6CB-20E6D1E799D8}" name="Breakfast" dataDxfId="26"/>
+    <tableColumn id="12" xr3:uid="{D37C5B0D-12C6-4CB3-BB80-08C12E6E49B6}" name="Lunch" dataDxfId="25"/>
+    <tableColumn id="13" xr3:uid="{E25F656B-1F18-455E-87D7-5C9D9B0097A5}" name="Dinner" dataDxfId="24"/>
+    <tableColumn id="17" xr3:uid="{BA985DFD-A4E6-404F-8823-002672B31C18}" name="Light Meal" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{A034FE6E-ED0A-4EFB-8D1C-030735AED3C9}" name="Main Protein" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{AA4E79D0-DAC8-43FF-A045-39E8C3C9F5CD}" name="Dish Role" dataDxfId="21"/>
+    <tableColumn id="15" xr3:uid="{3C0D36C0-00D9-469A-9A08-C9CBF82D88AE}" name="Taste" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{23809AC8-474B-40F8-84CF-2D42F7BE1C9D}" name="Expire(day)" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{FA20BD4E-AF4A-4273-8F29-845E2CF561A3}" name="Season" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{63A3F435-6F07-4F3F-B146-E824E495A1E4}" name="Credit to" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F96439F3-B3A1-473D-9915-B886E9B53018}" name="Ingredient" displayName="Ingredient" ref="A1:E122" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
-  <autoFilter ref="A1:E122" xr:uid="{F96439F3-B3A1-473D-9915-B886E9B53018}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{A6A630D5-6539-4FF3-B245-912977C8CE8E}" name="菜ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{7FF92CF3-2FA9-443E-A760-2445AFCE472F}" name="類別" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{B6463011-9D01-408A-B1FD-EFFF47425583}" name="材料" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{D7F5CA09-47D7-42CF-A952-E2A34C8C4E30}" name="份量" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{5A3FFFB1-F501-42BF-9602-AEB98CE8DA0C}" name="單位" dataDxfId="7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F96439F3-B3A1-473D-9915-B886E9B53018}" name="Ingredient" displayName="Ingredient" ref="A1:F128" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38">
+  <autoFilter ref="A1:F128" xr:uid="{F96439F3-B3A1-473D-9915-B886E9B53018}"/>
+  <tableColumns count="6">
+    <tableColumn id="6" xr3:uid="{58A7CCA8-AF26-4A8B-A664-D4C96E7F3BA0}" name="菜名" dataDxfId="1">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(B2,表格1[ID],表格1[Dish])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="1" xr3:uid="{A6A630D5-6539-4FF3-B245-912977C8CE8E}" name="菜ID" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{7FF92CF3-2FA9-443E-A760-2445AFCE472F}" name="類別" dataDxfId="36"/>
+    <tableColumn id="3" xr3:uid="{B6463011-9D01-408A-B1FD-EFFF47425583}" name="材料" dataDxfId="35"/>
+    <tableColumn id="4" xr3:uid="{D7F5CA09-47D7-42CF-A952-E2A34C8C4E30}" name="份量" dataDxfId="34"/>
+    <tableColumn id="5" xr3:uid="{5A3FFFB1-F501-42BF-9602-AEB98CE8DA0C}" name="單位" dataDxfId="33"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2074EDE5-B150-4BED-8B77-BE077FDDFB58}" name="Steps" displayName="Steps" ref="A1:C54" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
-  <autoFilter ref="A1:C54" xr:uid="{2074EDE5-B150-4BED-8B77-BE077FDDFB58}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{AC7DEC1F-B731-454F-AA1D-E750167F5368}" name="菜ID" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{2744473D-171F-4C43-A114-19D6A681227C}" name="步驟" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{20B9130A-A6FF-4BB1-87D8-CC9721812699}" name="內容" dataDxfId="2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2074EDE5-B150-4BED-8B77-BE077FDDFB58}" name="Steps" displayName="Steps" ref="A1:G60" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A1:G60" xr:uid="{2074EDE5-B150-4BED-8B77-BE077FDDFB58}"/>
+  <tableColumns count="7">
+    <tableColumn id="7" xr3:uid="{8937EE16-F967-45A6-AF51-C240F6B491BF}" name="菜名" dataDxfId="0">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(B2,表格1[ID],表格1[Dish])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="1" xr3:uid="{AC7DEC1F-B731-454F-AA1D-E750167F5368}" name="菜ID" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{2744473D-171F-4C43-A114-19D6A681227C}" name="步驟" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{20B9130A-A6FF-4BB1-87D8-CC9721812699}" name="內容" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{411CC2E6-8569-4ECA-98BF-CCC04F47DC15}" name="Step_EN" dataDxfId="4">
+      <calculatedColumnFormula>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{22A65150-E75D-4C7D-8847-4B10A2AB24D8}" name="Step_FIL" dataDxfId="3">
+      <calculatedColumnFormula>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{35BFC7E5-F93E-4F1D-8329-895464FC606A}" name="Step_ID" dataDxfId="2">
+      <calculatedColumnFormula>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{9B73EB78-A9E2-4560-A3F8-B02077E7EB70}" name="ingredient_unit" displayName="ingredient_unit" ref="A1:F71" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33">
-  <autoFilter ref="A1:F71" xr:uid="{9B73EB78-A9E2-4560-A3F8-B02077E7EB70}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{9B73EB78-A9E2-4560-A3F8-B02077E7EB70}" name="ingredient_unit" displayName="ingredient_unit" ref="A1:F74" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="A1:F74" xr:uid="{9B73EB78-A9E2-4560-A3F8-B02077E7EB70}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F50">
     <sortCondition ref="A1:A50"/>
   </sortState>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{D45EE57C-5C1F-42B3-A305-D4C61E8DF2E9}" name="材料"/>
-    <tableColumn id="2" xr3:uid="{C40C7E82-CCDD-408C-84C3-2A14B1ABC4C5}" name="英文" dataDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{6E0DB701-5A73-4C5B-A78A-67E14A93CA5C}" name="Filipino" dataDxfId="1">
+    <tableColumn id="2" xr3:uid="{C40C7E82-CCDD-408C-84C3-2A14B1ABC4C5}" name="英文" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{6E0DB701-5A73-4C5B-A78A-67E14A93CA5C}" name="Filipino" dataDxfId="8">
       <calculatedColumnFormula>_xlfn.TRANSLATE(ingredient_unit[[#This Row],[材料]],"zh-cht","fil")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{DB27FC22-78DB-4C93-BC55-A2A340CDB570}" name="Bahasa" dataDxfId="0">
+    <tableColumn id="4" xr3:uid="{DB27FC22-78DB-4C93-BC55-A2A340CDB570}" name="Bahasa" dataDxfId="7">
       <calculatedColumnFormula>_xlfn.TRANSLATE(ingredient_unit[[#This Row],[材料]],"zh-cht","id")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{3103CB67-8224-4FF9-B0D4-00AF214CE6C9}" name="類別" dataDxfId="31"/>
-    <tableColumn id="6" xr3:uid="{7F65B4DE-DCF1-4E5A-954A-E2A0F11C54CB}" name="常用單位" dataDxfId="30"/>
+    <tableColumn id="5" xr3:uid="{3103CB67-8224-4FF9-B0D4-00AF214CE6C9}" name="類別" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{7F65B4DE-DCF1-4E5A-954A-E2A0F11C54CB}" name="常用單位" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9402,7 +9523,7 @@
       <c r="C81" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D81" s="1" t="s">
+      <c r="D81" s="6" t="s">
         <v>103</v>
       </c>
       <c r="E81" s="1" t="s">
@@ -12852,7 +12973,7 @@
       </c>
     </row>
     <row r="192" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A192" s="1" t="s">
+      <c r="A192" s="9" t="s">
         <v>734</v>
       </c>
       <c r="B192" s="1" t="s">
@@ -12969,7 +13090,7 @@
       </c>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A195" s="1" t="s">
+      <c r="A195" s="9" t="s">
         <v>737</v>
       </c>
       <c r="B195" s="1" t="s">
@@ -15396,2051 +15517,2701 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C0D18FD-706B-423D-A1C9-E7D4E7EB4348}">
-  <dimension ref="A1:E122"/>
+  <dimension ref="A1:F128"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="2" width="8.7265625" style="1"/>
-    <col min="3" max="3" width="14.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.7265625" style="1"/>
+    <col min="1" max="1" width="21.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="8.7265625" style="1"/>
+    <col min="4" max="4" width="14.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A1" s="20" t="s">
+        <v>873</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="C1" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B2,表格1[ID],表格1[Dish])</f>
+        <v>燕麥蒸肉餅</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="D2" s="1">
+      <c r="E2" s="1">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B3,表格1[ID],表格1[Dish])</f>
+        <v>燕麥蒸肉餅</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="D3" s="1">
+      <c r="E3" s="1">
         <v>2</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A4" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B4,表格1[ID],表格1[Dish])</f>
+        <v>燕麥蒸肉餅</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="D4" s="1">
+      <c r="E4" s="1">
         <v>120</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B5,表格1[ID],表格1[Dish])</f>
+        <v>燕麥蒸肉餅</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="D5" s="1">
+      <c r="E5" s="1">
         <v>0.5</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A6" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B6,表格1[ID],表格1[Dish])</f>
+        <v>燕麥蒸肉餅</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="D6" s="1">
+      <c r="E6" s="1">
         <v>0.5</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A7" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B7,表格1[ID],表格1[Dish])</f>
+        <v>燕麥蒸肉餅</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="D7" s="1">
+      <c r="E7" s="1">
         <v>0.5</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A8" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B8,表格1[ID],表格1[Dish])</f>
+        <v>燕麥蒸肉餅</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="D8" s="1">
+      <c r="E8" s="1">
         <v>1</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B9,表格1[ID],表格1[Dish])</f>
+        <v>燕麥蒸肉餅</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A10" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B10,表格1[ID],表格1[Dish])</f>
+        <v>椰青木瓜果凍</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="D10" s="1">
+      <c r="E10" s="1">
         <v>0.5</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A11" s="1" t="s">
+    <row r="11" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A11" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B11,表格1[ID],表格1[Dish])</f>
+        <v>椰青木瓜果凍</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="D11" s="1">
+      <c r="E11" s="1">
         <v>200</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A12" s="1" t="s">
+    <row r="12" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A12" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B12,表格1[ID],表格1[Dish])</f>
+        <v>椰青木瓜果凍</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D12" s="1">
+      <c r="E12" s="1">
         <v>250</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A13" s="1" t="s">
+    <row r="13" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A13" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B13,表格1[ID],表格1[Dish])</f>
+        <v>椰青木瓜果凍</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="D13" s="1">
+      <c r="E13" s="1">
         <v>5</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A14" s="1" t="s">
+    <row r="14" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A14" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B14,表格1[ID],表格1[Dish])</f>
+        <v>椰青木瓜果凍</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="D14" s="1">
+      <c r="E14" s="1">
         <v>30</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A15" s="1" t="s">
+    <row r="15" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A15" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B15,表格1[ID],表格1[Dish])</f>
+        <v>紫薯布甸</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="C15" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="D15" s="1">
+      <c r="E15" s="1">
         <v>300</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A16" s="1" t="s">
+    <row r="16" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A16" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B16,表格1[ID],表格1[Dish])</f>
+        <v>紫薯布甸</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="D16" s="1">
+      <c r="E16" s="1">
         <v>200</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="F16" s="1" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A17" s="1" t="s">
+    <row r="17" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A17" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B17,表格1[ID],表格1[Dish])</f>
+        <v>紫薯布甸</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="C17" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="D17" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="D17" s="1">
+      <c r="E17" s="1">
         <v>300</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="F17" s="1" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A18" s="1" t="s">
+    <row r="18" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A18" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B18,表格1[ID],表格1[Dish])</f>
+        <v>紫薯布甸</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="C18" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="D18" s="1">
+      <c r="E18" s="1">
         <v>50</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="F18" s="1" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A19" s="1" t="s">
+    <row r="19" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A19" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B19,表格1[ID],表格1[Dish])</f>
+        <v>紫薯布甸</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="C19" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="D19" s="1">
+      <c r="E19" s="1">
         <v>3</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="F19" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A20" s="1" t="s">
+    <row r="20" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A20" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B20,表格1[ID],表格1[Dish])</f>
+        <v>焗葡汁白菌豆腐飯</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="C20" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="D20" s="1">
+      <c r="E20" s="1">
         <v>2</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="F20" s="1" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A21" s="1" t="s">
+    <row r="21" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A21" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B21,表格1[ID],表格1[Dish])</f>
+        <v>焗葡汁白菌豆腐飯</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="C21" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="D21" s="1">
+      <c r="E21" s="1">
         <v>0.5</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="F21" s="1" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A22" s="1" t="s">
+    <row r="22" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A22" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B22,表格1[ID],表格1[Dish])</f>
+        <v>焗葡汁白菌豆腐飯</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D22" s="1">
+      <c r="E22" s="1">
         <v>1</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A23" s="1" t="s">
+    <row r="23" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A23" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B23,表格1[ID],表格1[Dish])</f>
+        <v>焗葡汁白菌豆腐飯</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="C23" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="D23" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="D23" s="1">
+      <c r="E23" s="1">
         <v>2</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A24" s="1" t="s">
+    <row r="24" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A24" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B24,表格1[ID],表格1[Dish])</f>
+        <v>焗葡汁白菌豆腐飯</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="C24" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="D24" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="D24" s="1">
+      <c r="E24" s="1">
         <v>250</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="F24" s="1" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A25" s="1" t="s">
+    <row r="25" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A25" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B25,表格1[ID],表格1[Dish])</f>
+        <v>焗葡汁白菌豆腐飯</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="C25" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="D25" s="1">
+      <c r="E25" s="1">
         <v>100</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="F25" s="1" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A26" s="1" t="s">
+    <row r="26" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A26" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B26,表格1[ID],表格1[Dish])</f>
+        <v>焗葡汁白菌豆腐飯</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="C26" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="D26" s="1">
+      <c r="E26" s="1">
         <v>120</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="F26" s="1" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A27" s="1" t="s">
+    <row r="27" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A27" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B27,表格1[ID],表格1[Dish])</f>
+        <v>焗葡汁白菌豆腐飯</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="C27" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="D27" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="D27" s="1">
+      <c r="E27" s="1">
         <v>2</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="F27" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A28" s="1" t="s">
+    <row r="28" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A28" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B28,表格1[ID],表格1[Dish])</f>
+        <v>焗葡汁白菌豆腐飯</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="C28" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="D28" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="E28" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="F28" s="1" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A29" s="1" t="s">
+    <row r="29" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A29" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B29,表格1[ID],表格1[Dish])</f>
+        <v>焗葡汁白菌豆腐飯</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="C29" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="E29" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="F29" s="1" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A30" s="1" t="s">
+    <row r="30" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A30" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B30,表格1[ID],表格1[Dish])</f>
+        <v>焗葡汁白菌豆腐飯</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="C30" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="D30" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="D30" s="1">
+      <c r="E30" s="1">
         <v>0.5</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="F30" s="1" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A31" s="1" t="s">
+    <row r="31" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A31" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B31,表格1[ID],表格1[Dish])</f>
+        <v>焗葡汁白菌豆腐飯</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="C31" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="D31" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D31" s="1">
+      <c r="E31" s="1">
         <v>1.5</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="F31" s="1" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A32" s="1" t="s">
+    <row r="32" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A32" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B32,表格1[ID],表格1[Dish])</f>
+        <v>焗葡汁白菌豆腐飯</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="C32" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="D32" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="D32" s="1">
+      <c r="E32" s="1">
         <v>2</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="F32" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A33" s="1" t="s">
+    <row r="33" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A33" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B33,表格1[ID],表格1[Dish])</f>
+        <v>焗葡汁白菌豆腐飯</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="C33" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="D33" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="E33" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="F33" s="1" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A34" s="1" t="s">
+    <row r="34" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A34" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B34,表格1[ID],表格1[Dish])</f>
+        <v>焗葡汁白菌豆腐飯</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="C34" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="D34" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D34" s="1">
+      <c r="E34" s="1">
         <v>2</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="F34" s="1" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A35" s="1" t="s">
+    <row r="35" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A35" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B35,表格1[ID],表格1[Dish])</f>
+        <v>焗葡汁白菌豆腐飯</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="C35" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="D35" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="D35" s="1">
+      <c r="E35" s="1">
         <v>2</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="F35" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A36" s="1" t="s">
+    <row r="36" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A36" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B36,表格1[ID],表格1[Dish])</f>
+        <v>素羅宋湯</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="C36" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="D36" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="D36" s="1">
+      <c r="E36" s="1">
         <v>3</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="F36" s="1" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A37" s="1" t="s">
+    <row r="37" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A37" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B37,表格1[ID],表格1[Dish])</f>
+        <v>素羅宋湯</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="C37" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="D37" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="D37" s="1">
+      <c r="E37" s="1">
         <v>1</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="F37" s="1" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A38" s="1" t="s">
+    <row r="38" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A38" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B38,表格1[ID],表格1[Dish])</f>
+        <v>素羅宋湯</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="C38" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="D38" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="D38" s="1">
+      <c r="E38" s="1">
         <v>1</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="F38" s="1" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A39" s="1" t="s">
+    <row r="39" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A39" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B39,表格1[ID],表格1[Dish])</f>
+        <v>素羅宋湯</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="C39" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="D39" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="D39" s="1">
+      <c r="E39" s="1">
         <v>0.5</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="F39" s="1" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A40" s="1" t="s">
+    <row r="40" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A40" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B40,表格1[ID],表格1[Dish])</f>
+        <v>素羅宋湯</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="C40" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="D40" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="D40" s="1">
+      <c r="E40" s="1">
         <v>0.5</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="F40" s="1" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A41" s="1" t="s">
+    <row r="41" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A41" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B41,表格1[ID],表格1[Dish])</f>
+        <v>素羅宋湯</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="C41" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="D41" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="D41" s="1">
+      <c r="E41" s="1">
         <v>2</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="F41" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A42" s="1" t="s">
+    <row r="42" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A42" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B42,表格1[ID],表格1[Dish])</f>
+        <v>素羅宋湯</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="C42" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="D42" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="D42" s="1">
+      <c r="E42" s="1">
         <v>2</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="F42" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A43" s="1" t="s">
+    <row r="43" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A43" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B43,表格1[ID],表格1[Dish])</f>
+        <v>素羅宋湯</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="C43" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="D43" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="D43" s="1">
+      <c r="E43" s="1">
         <v>1</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="F43" s="1" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A44" s="1" t="s">
+    <row r="44" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A44" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B44,表格1[ID],表格1[Dish])</f>
+        <v>素羅宋湯</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="C44" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="D44" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="D44" s="1">
+      <c r="E44" s="1">
         <v>2</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="F44" s="1" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A45" s="1" t="s">
+    <row r="45" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A45" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B45,表格1[ID],表格1[Dish])</f>
+        <v>素羅宋湯</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="C45" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="D45" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="D45" s="1">
+      <c r="E45" s="1">
         <v>2</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="F45" s="1" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A46" s="1" t="s">
+    <row r="46" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A46" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B46,表格1[ID],表格1[Dish])</f>
+        <v>素羅宋湯</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="C46" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="D46" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="E46" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="F46" s="1" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A47" s="1" t="s">
+    <row r="47" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A47" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B47,表格1[ID],表格1[Dish])</f>
+        <v>薯仔沙律蛋包</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="C47" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="D47" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="D47" s="1">
+      <c r="E47" s="1">
         <v>2</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="F47" s="1" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A48" s="1" t="s">
+    <row r="48" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A48" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B48,表格1[ID],表格1[Dish])</f>
+        <v>薯仔沙律蛋包</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="C48" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="D48" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="D48" s="1">
+      <c r="E48" s="1">
         <v>2</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="F48" s="1" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A49" s="1" t="s">
+    <row r="49" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A49" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B49,表格1[ID],表格1[Dish])</f>
+        <v>薯仔沙律蛋包</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="C49" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="D49" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="D49" s="1">
+      <c r="E49" s="1">
         <v>1</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="F49" s="1" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A50" s="1" t="s">
+    <row r="50" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A50" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B50,表格1[ID],表格1[Dish])</f>
+        <v>薯仔沙律蛋包</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="C50" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="D50" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="D50" s="1">
+      <c r="E50" s="1">
         <v>1</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="F50" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A51" s="1" t="s">
+    <row r="51" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A51" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B51,表格1[ID],表格1[Dish])</f>
+        <v>薯仔沙律蛋包</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="C51" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="D51" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="D51" s="1">
+      <c r="E51" s="1">
         <v>1</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="F51" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A52" s="1" t="s">
+    <row r="52" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A52" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B52,表格1[ID],表格1[Dish])</f>
+        <v>薯仔沙律蛋包</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="C52" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="D52" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="E52" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="F52" s="1" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A53" s="1" t="s">
+    <row r="53" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A53" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B53,表格1[ID],表格1[Dish])</f>
+        <v>薯仔沙律蛋包</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="C53" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="D53" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="D53" s="1">
+      <c r="E53" s="1">
         <v>2</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="F53" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A54" s="1" t="s">
+    <row r="54" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A54" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B54,表格1[ID],表格1[Dish])</f>
+        <v>薯仔沙律蛋包</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="C54" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="D54" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="D54" s="1">
+      <c r="E54" s="1">
         <v>0.5</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="F54" s="1" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A55" s="1" t="s">
+    <row r="55" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A55" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B55,表格1[ID],表格1[Dish])</f>
+        <v>薯仔沙律蛋包</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="C55" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="D55" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="D55" s="1">
+      <c r="E55" s="1">
         <v>1</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="F55" s="1" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A56" s="1" t="s">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A56" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B56,表格1[ID],表格1[Dish])</f>
+        <v>麻婆豆腐</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="C56" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="D56" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="D56" s="1">
+      <c r="E56" s="1">
         <v>100</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="F56" s="1" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A57" s="1" t="s">
+    <row r="57" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A57" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B57,表格1[ID],表格1[Dish])</f>
+        <v>麻婆豆腐</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="C57" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="D57" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="D57" s="1">
+      <c r="E57" s="1">
         <v>1</v>
       </c>
-      <c r="E57" s="1" t="s">
+      <c r="F57" s="1" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A58" s="1" t="s">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A58" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B58,表格1[ID],表格1[Dish])</f>
+        <v>麻婆豆腐</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="C58" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="D58" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="D58" s="1">
+      <c r="E58" s="1">
         <v>20</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="F58" s="1" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A59" s="1" t="s">
+    <row r="59" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A59" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B59,表格1[ID],表格1[Dish])</f>
+        <v>麻婆豆腐</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="C59" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="D59" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="D59" s="1">
+      <c r="E59" s="1">
         <v>1</v>
       </c>
-      <c r="E59" s="1" t="s">
+      <c r="F59" s="1" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A60" s="1" t="s">
+    <row r="60" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A60" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B60,表格1[ID],表格1[Dish])</f>
+        <v>麻婆豆腐</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="C60" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="D60" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="D60" s="1">
+      <c r="E60" s="1">
         <v>1</v>
       </c>
-      <c r="E60" s="1" t="s">
+      <c r="F60" s="1" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A61" s="1" t="s">
+    <row r="61" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A61" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B61,表格1[ID],表格1[Dish])</f>
+        <v>麻婆豆腐</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="C61" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="D61" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="D61" s="1">
+      <c r="E61" s="1">
         <v>1</v>
       </c>
-      <c r="E61" s="1" t="s">
+      <c r="F61" s="1" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A62" s="1" t="s">
+    <row r="62" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A62" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B62,表格1[ID],表格1[Dish])</f>
+        <v>麻婆豆腐</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="C62" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="D62" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="D62" s="1">
+      <c r="E62" s="1">
         <v>1</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="F62" s="1" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A63" s="1" t="s">
+    <row r="63" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A63" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B63,表格1[ID],表格1[Dish])</f>
+        <v>麻婆豆腐</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="C63" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="D63" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="D63" s="1">
+      <c r="E63" s="1">
         <v>1</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="F63" s="1" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A64" s="1" t="s">
+    <row r="64" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A64" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B64,表格1[ID],表格1[Dish])</f>
+        <v>麻婆豆腐</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="C64" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="D64" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="D64" s="1">
+      <c r="E64" s="1">
         <v>2</v>
       </c>
-      <c r="E64" s="1" t="s">
+      <c r="F64" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A65" s="1" t="s">
+    <row r="65" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A65" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B65,表格1[ID],表格1[Dish])</f>
+        <v>麻婆豆腐</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="C65" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="D65" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="D65" s="1">
+      <c r="E65" s="1">
         <v>1</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="F65" s="1" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A66" s="1" t="s">
+    <row r="66" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A66" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B66,表格1[ID],表格1[Dish])</f>
+        <v>麻婆豆腐</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="C66" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="D66" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="D66" s="1">
+      <c r="E66" s="1">
         <v>1</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="F66" s="1" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A67" s="1" t="s">
+    <row r="67" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A67" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B67,表格1[ID],表格1[Dish])</f>
+        <v>麻婆豆腐</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="C67" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="D67" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="E67" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="E67" s="1" t="s">
+      <c r="F67" s="1" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A68" s="1" t="s">
+    <row r="68" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A68" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B68,表格1[ID],表格1[Dish])</f>
+        <v>麻婆豆腐</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="C68" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="D68" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="D68" s="1">
+      <c r="E68" s="1">
         <v>0.5</v>
       </c>
-      <c r="E68" s="1" t="s">
+      <c r="F68" s="1" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A69" s="1" t="s">
+    <row r="69" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A69" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B69,表格1[ID],表格1[Dish])</f>
+        <v>麻婆豆腐</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="C69" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="D69" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="D69" s="1">
+      <c r="E69" s="1">
         <v>1</v>
       </c>
-      <c r="E69" s="1" t="s">
+      <c r="F69" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A70" s="1" t="s">
+    <row r="70" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A70" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B70,表格1[ID],表格1[Dish])</f>
+        <v>蒜蓉蒸茄子</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="C70" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="D70" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="D70" s="1">
+      <c r="E70" s="1">
         <v>1</v>
       </c>
-      <c r="E70" s="1" t="s">
+      <c r="F70" s="1" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A71" s="1" t="s">
+    <row r="71" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A71" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B71,表格1[ID],表格1[Dish])</f>
+        <v>蒜蓉蒸茄子</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="C71" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="D71" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="D71" s="1">
+      <c r="E71" s="1">
         <v>0.5</v>
       </c>
-      <c r="E71" s="1" t="s">
+      <c r="F71" s="1" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A72" s="1" t="s">
+    <row r="72" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A72" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B72,表格1[ID],表格1[Dish])</f>
+        <v>蒜蓉蒸茄子</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="C72" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="D72" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="D72" s="1">
+      <c r="E72" s="1">
         <v>1</v>
       </c>
-      <c r="E72" s="1" t="s">
+      <c r="F72" s="1" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A73" s="1" t="s">
+    <row r="73" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A73" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B73,表格1[ID],表格1[Dish])</f>
+        <v>蒜蓉蒸茄子</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="C73" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="D73" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="D73" s="1">
+      <c r="E73" s="1">
         <v>0.5</v>
       </c>
-      <c r="E73" s="2" t="s">
+      <c r="F73" s="2" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A74" s="1" t="s">
+    <row r="74" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A74" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B74,表格1[ID],表格1[Dish])</f>
+        <v>蒜蓉蒸茄子</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="C74" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="D74" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D74" s="1">
+      <c r="E74" s="1">
         <v>1</v>
       </c>
-      <c r="E74" s="2" t="s">
+      <c r="F74" s="2" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A75" s="1" t="s">
+    <row r="75" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A75" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B75,表格1[ID],表格1[Dish])</f>
+        <v>蒜蓉蒸茄子</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="C75" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="D75" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="D75" s="1">
+      <c r="E75" s="1">
         <v>0.5</v>
       </c>
-      <c r="E75" s="2" t="s">
+      <c r="F75" s="2" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A76" s="1" t="s">
+    <row r="76" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A76" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B76,表格1[ID],表格1[Dish])</f>
+        <v>蒜蓉蒸茄子</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="C76" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="D76" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="E76" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="E76" s="1" t="s">
+      <c r="F76" s="1" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A77" s="1" t="s">
+    <row r="77" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A77" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B77,表格1[ID],表格1[Dish])</f>
+        <v>金銀蛋菠菜</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="C77" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="D77" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="D77" s="1">
+      <c r="E77" s="1">
         <v>2</v>
       </c>
-      <c r="E77" s="2" t="s">
+      <c r="F77" s="2" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A78" s="1" t="s">
+    <row r="78" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A78" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B78,表格1[ID],表格1[Dish])</f>
+        <v>金銀蛋菠菜</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="C78" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="D78" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="D78" s="1">
+      <c r="E78" s="1">
         <v>2</v>
       </c>
-      <c r="E78" s="2" t="s">
+      <c r="F78" s="2" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A79" s="1" t="s">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A79" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B79,表格1[ID],表格1[Dish])</f>
+        <v>金銀蛋菠菜</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="C79" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="D79" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="D79" s="1">
+      <c r="E79" s="1">
         <v>500</v>
       </c>
-      <c r="E79" s="1" t="s">
+      <c r="F79" s="1" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A80" s="1" t="s">
+    <row r="80" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A80" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B80,表格1[ID],表格1[Dish])</f>
+        <v>金銀蛋菠菜</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="C80" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="D80" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="D80" s="1">
+      <c r="E80" s="1">
         <v>1</v>
       </c>
-      <c r="E80" s="2" t="s">
+      <c r="F80" s="2" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A81" s="1" t="s">
+    <row r="81" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A81" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B81,表格1[ID],表格1[Dish])</f>
+        <v>金銀蛋菠菜</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="C81" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="D81" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="D81" s="1">
+      <c r="E81" s="1">
         <v>4</v>
       </c>
-      <c r="E81" s="2" t="s">
+      <c r="F81" s="2" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A82" s="1" t="s">
+    <row r="82" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A82" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B82,表格1[ID],表格1[Dish])</f>
+        <v>薑葱焗桶蠔</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="C82" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="D82" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="D82" s="1">
+      <c r="E82" s="1">
         <v>1</v>
       </c>
-      <c r="E82" s="2" t="s">
+      <c r="F82" s="2" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A83" s="1" t="s">
+    <row r="83" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A83" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B83,表格1[ID],表格1[Dish])</f>
+        <v>薑葱焗桶蠔</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="C83" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="D83" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="D83" s="1">
+      <c r="E83" s="1">
         <v>4</v>
       </c>
-      <c r="E83" s="2" t="s">
+      <c r="F83" s="2" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A84" s="1" t="s">
+    <row r="84" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A84" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B84,表格1[ID],表格1[Dish])</f>
+        <v>薑葱焗桶蠔</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="C84" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="D84" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D84" s="1">
+      <c r="E84" s="1">
         <v>8</v>
       </c>
-      <c r="E84" s="2" t="s">
+      <c r="F84" s="2" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A85" s="1" t="s">
+    <row r="85" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A85" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B85,表格1[ID],表格1[Dish])</f>
+        <v>薑葱焗桶蠔</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="C85" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="D85" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="D85" s="1">
+      <c r="E85" s="1">
         <v>4</v>
       </c>
-      <c r="E85" s="2" t="s">
+      <c r="F85" s="2" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A86" s="1" t="s">
+    <row r="86" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A86" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B86,表格1[ID],表格1[Dish])</f>
+        <v>薑葱焗桶蠔</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="C86" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="D86" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="D86" s="1">
+      <c r="E86" s="1">
         <v>1</v>
       </c>
-      <c r="E86" s="2" t="s">
+      <c r="F86" s="2" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A87" s="1" t="s">
+    <row r="87" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A87" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B87,表格1[ID],表格1[Dish])</f>
+        <v>薑葱焗桶蠔</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="C87" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="D87" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="D87" s="1">
+      <c r="E87" s="1">
         <v>0.5</v>
       </c>
-      <c r="E87" s="2" t="s">
+      <c r="F87" s="2" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A88" s="1" t="s">
+    <row r="88" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A88" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B88,表格1[ID],表格1[Dish])</f>
+        <v>薑葱焗桶蠔</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="C88" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="D88" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="D88" s="1">
+      <c r="E88" s="1">
         <v>0.5</v>
       </c>
-      <c r="E88" s="2" t="s">
+      <c r="F88" s="2" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A89" s="1" t="s">
+    <row r="89" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A89" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B89,表格1[ID],表格1[Dish])</f>
+        <v>薑葱焗桶蠔</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="C89" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="D89" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D89" s="1">
+      <c r="E89" s="1">
         <v>5</v>
       </c>
-      <c r="E89" s="2" t="s">
+      <c r="F89" s="2" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A90" s="1" t="s">
+    <row r="90" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A90" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B90,表格1[ID],表格1[Dish])</f>
+        <v>薑葱焗桶蠔</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="C90" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="D90" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D90" s="1" t="s">
+      <c r="E90" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="E90" s="1" t="s">
+      <c r="F90" s="1" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A91" s="1" t="s">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A91" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B91,表格1[ID],表格1[Dish])</f>
+        <v>薑葱焗桶蠔</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="C91" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="D91" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D91" s="1">
+      <c r="E91" s="1">
         <v>1</v>
       </c>
-      <c r="E91" s="1" t="s">
+      <c r="F91" s="1" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A92" s="1" t="s">
+    <row r="92" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A92" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B92,表格1[ID],表格1[Dish])</f>
+        <v>薑葱焗桶蠔</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="C92" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="D92" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="D92" s="1">
+      <c r="E92" s="1">
         <v>2</v>
       </c>
-      <c r="E92" s="2" t="s">
+      <c r="F92" s="2" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A93" s="1" t="s">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A93" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B93,表格1[ID],表格1[Dish])</f>
+        <v>土匪雞翼</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="C93" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="D93" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="D93" s="1">
+      <c r="E93" s="1">
         <v>0.5</v>
       </c>
-      <c r="E93" s="1" t="s">
+      <c r="F93" s="1" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A94" s="1" t="s">
+    <row r="94" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A94" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B94,表格1[ID],表格1[Dish])</f>
+        <v>土匪雞翼</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="C94" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="D94" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="D94" s="1" t="s">
+      <c r="E94" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="E94" s="1" t="s">
+      <c r="F94" s="1" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A95" s="1" t="s">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A95" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B95,表格1[ID],表格1[Dish])</f>
+        <v>土匪雞翼</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="C95" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="D95" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="D95" s="1">
+      <c r="E95" s="1">
         <v>3</v>
       </c>
-      <c r="E95" s="1" t="s">
+      <c r="F95" s="1" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A96" s="1" t="s">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A96" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B96,表格1[ID],表格1[Dish])</f>
+        <v>土匪雞翼</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="C96" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="D96" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="D96" s="1">
+      <c r="E96" s="1">
         <v>1</v>
       </c>
-      <c r="E96" s="1" t="s">
+      <c r="F96" s="1" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A97" s="1" t="s">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A97" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B97,表格1[ID],表格1[Dish])</f>
+        <v>土匪雞翼</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="C97" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="D97" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="D97" s="1">
+      <c r="E97" s="1">
         <v>1</v>
       </c>
-      <c r="E97" s="1" t="s">
+      <c r="F97" s="1" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A98" s="1" t="s">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A98" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B98,表格1[ID],表格1[Dish])</f>
+        <v>土匪雞翼</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="C98" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="D98" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="D98" s="1">
+      <c r="E98" s="1">
         <v>1</v>
       </c>
-      <c r="E98" s="1" t="s">
+      <c r="F98" s="1" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A99" s="1" t="s">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A99" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B99,表格1[ID],表格1[Dish])</f>
+        <v>土匪雞翼</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="C99" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="D99" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="D99" s="1">
+      <c r="E99" s="1">
         <v>2</v>
       </c>
-      <c r="E99" s="1" t="s">
+      <c r="F99" s="1" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A100" s="1" t="s">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A100" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B100,表格1[ID],表格1[Dish])</f>
+        <v>土匪雞翼</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="C100" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="D100" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="D100" s="1">
+      <c r="E100" s="1">
         <v>1</v>
       </c>
-      <c r="E100" s="1" t="s">
+      <c r="F100" s="1" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A101" s="1" t="s">
+    <row r="101" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A101" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B101,表格1[ID],表格1[Dish])</f>
+        <v>土匪雞翼</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="C101" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="D101" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="D101" s="1">
+      <c r="E101" s="1">
         <v>2</v>
       </c>
-      <c r="E101" s="2" t="s">
+      <c r="F101" s="2" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A102" s="1" t="s">
+    <row r="102" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A102" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B102,表格1[ID],表格1[Dish])</f>
+        <v>涼伴雲耳</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="C102" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="D102" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="D102">
+      <c r="E102">
         <v>1</v>
       </c>
-      <c r="E102" t="s">
+      <c r="F102" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A103" s="1" t="s">
+    <row r="103" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A103" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B103,表格1[ID],表格1[Dish])</f>
+        <v>涼伴雲耳</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="C103" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C103" s="1" t="s">
+      <c r="D103" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="D103">
+      <c r="E103">
         <v>1</v>
       </c>
-      <c r="E103" t="s">
+      <c r="F103" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A104" s="1" t="s">
+    <row r="104" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A104" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B104,表格1[ID],表格1[Dish])</f>
+        <v>涼伴雲耳</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B104" s="1" t="s">
+      <c r="C104" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C104" s="1" t="s">
+      <c r="D104" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="D104">
+      <c r="E104">
         <v>1</v>
       </c>
-      <c r="E104" t="s">
+      <c r="F104" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A105" s="1" t="s">
+    <row r="105" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A105" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B105,表格1[ID],表格1[Dish])</f>
+        <v>涼伴雲耳</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="C105" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="D105" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="D105">
+      <c r="E105">
         <v>1</v>
       </c>
-      <c r="E105" t="s">
+      <c r="F105" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A106" s="1" t="s">
+    <row r="106" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A106" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B106,表格1[ID],表格1[Dish])</f>
+        <v>涼伴雲耳</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B106" s="1" t="s">
+      <c r="C106" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C106" s="1" t="s">
+      <c r="D106" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="D106">
+      <c r="E106">
         <v>1</v>
       </c>
-      <c r="E106" t="s">
+      <c r="F106" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A107" s="1" t="s">
+    <row r="107" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A107" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B107,表格1[ID],表格1[Dish])</f>
+        <v>涼伴雲耳</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="C107" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C107" s="1" t="s">
+      <c r="D107" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="D107">
+      <c r="E107">
         <v>1</v>
       </c>
-      <c r="E107" t="s">
+      <c r="F107" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A108" s="1" t="s">
+    <row r="108" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A108" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B108,表格1[ID],表格1[Dish])</f>
+        <v>涼伴雲耳</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B108" s="1" t="s">
+      <c r="C108" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C108" s="1" t="s">
+      <c r="D108" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="D108">
+      <c r="E108">
         <v>1</v>
       </c>
-      <c r="E108" t="s">
+      <c r="F108" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A109" s="1" t="s">
+    <row r="109" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A109" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B109,表格1[ID],表格1[Dish])</f>
+        <v>涼伴雲耳</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="C109" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="D109" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="D109">
+      <c r="E109">
         <v>1</v>
       </c>
-      <c r="E109" t="s">
+      <c r="F109" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A110" s="1" t="s">
+    <row r="110" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A110" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B110,表格1[ID],表格1[Dish])</f>
+        <v>涼伴雲耳</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="C110" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C110" s="1" t="s">
+      <c r="D110" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="D110" t="s">
+      <c r="E110" t="s">
         <v>366</v>
       </c>
-      <c r="E110" t="s">
+      <c r="F110" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A111" s="1" t="s">
+    <row r="111" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A111" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B111,表格1[ID],表格1[Dish])</f>
+        <v>醬燒豆腐</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="C111" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C111" s="1" t="s">
+      <c r="D111" s="1" t="s">
         <v>702</v>
       </c>
-      <c r="D111" s="1">
+      <c r="E111" s="1">
         <v>1</v>
       </c>
-      <c r="E111" s="2" t="s">
+      <c r="F111" s="2" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A112" s="1" t="s">
+    <row r="112" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A112" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B112,表格1[ID],表格1[Dish])</f>
+        <v>醬燒豆腐</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="C112" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C112" s="1" t="s">
+      <c r="D112" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="D112" s="1">
+      <c r="E112" s="1">
         <v>1</v>
       </c>
-      <c r="E112" s="2" t="s">
+      <c r="F112" s="2" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A113" s="1" t="s">
+    <row r="113" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A113" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B113,表格1[ID],表格1[Dish])</f>
+        <v>醬燒豆腐</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="C113" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C113" s="1" t="s">
+      <c r="D113" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="D113" s="1">
+      <c r="E113" s="1">
         <v>2</v>
       </c>
-      <c r="E113" s="2" t="s">
+      <c r="F113" s="2" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A114" s="1" t="s">
+    <row r="114" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A114" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B114,表格1[ID],表格1[Dish])</f>
+        <v>醬燒豆腐</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="B114" s="1" t="s">
+      <c r="C114" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C114" s="1" t="s">
+      <c r="D114" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="D114" s="1">
+      <c r="E114" s="1">
         <v>1</v>
       </c>
-      <c r="E114" s="2" t="s">
+      <c r="F114" s="2" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A115" s="1" t="s">
+    <row r="115" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A115" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B115,表格1[ID],表格1[Dish])</f>
+        <v>蒜香蒸豬五花高麗菜</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="B115" s="1" t="s">
+      <c r="C115" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C115" s="1" t="s">
+      <c r="D115" s="1" t="s">
         <v>861</v>
       </c>
-      <c r="D115" s="1">
+      <c r="E115" s="1">
         <v>0.25</v>
       </c>
-      <c r="E115" s="2" t="s">
+      <c r="F115" s="2" t="s">
         <v>862</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A116" s="1" t="s">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A116" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B116,表格1[ID],表格1[Dish])</f>
+        <v>蒜香蒸豬五花高麗菜</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="B116" s="1" t="s">
+      <c r="C116" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="D116" s="1" t="s">
         <v>863</v>
       </c>
-      <c r="D116" s="1">
+      <c r="E116" s="1">
         <v>200</v>
       </c>
-      <c r="E116" s="1" t="s">
+      <c r="F116" s="1" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A117" s="1" t="s">
+    <row r="117" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A117" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B117,表格1[ID],表格1[Dish])</f>
+        <v>蒜香蒸豬五花高麗菜</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="C117" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="D117" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="D117" s="1">
+      <c r="E117" s="1">
         <v>2</v>
       </c>
-      <c r="E117" s="2" t="s">
+      <c r="F117" s="2" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A118" s="1" t="s">
+    <row r="118" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A118" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B118,表格1[ID],表格1[Dish])</f>
+        <v>蒜香蒸豬五花高麗菜</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="C118" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="D118" s="1" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A119" s="1" t="s">
+      <c r="E118" s="1">
+        <v>1</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A119" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B119,表格1[ID],表格1[Dish])</f>
+        <v>蒜香蒸豬五花高麗菜</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="C119" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C119" s="1" t="s">
+      <c r="D119" s="1" t="s">
         <v>865</v>
       </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A120" s="1" t="s">
+      <c r="E119" s="1">
+        <v>1</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A120" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B120,表格1[ID],表格1[Dish])</f>
+        <v>蒜香蒸豬五花高麗菜</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="B120" s="1" t="s">
+      <c r="C120" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C120" s="1" t="s">
+      <c r="D120" s="1" t="s">
         <v>867</v>
       </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A121" s="1" t="s">
+      <c r="E120" s="1">
+        <v>1</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A121" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B121,表格1[ID],表格1[Dish])</f>
+        <v>蒜香蒸豬五花高麗菜</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="C121" s="1" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A122" s="1" t="s">
+      <c r="D121" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E121" s="1">
+        <v>2</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A122" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B122,表格1[ID],表格1[Dish])</f>
+        <v>蒜香蒸豬五花高麗菜</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="C122" s="1" t="s">
         <v>345</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A123" s="21" t="str">
+        <f>_xlfn.XLOOKUP(B123,表格1[ID],表格1[Dish])</f>
+        <v>豆腐肉捲</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="E123" s="1">
+        <v>200</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A124" s="21" t="str">
+        <f>_xlfn.XLOOKUP(B124,表格1[ID],表格1[Dish])</f>
+        <v>豆腐肉捲</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="E124" s="1">
+        <v>2</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A125" s="21" t="str">
+        <f>_xlfn.XLOOKUP(B125,表格1[ID],表格1[Dish])</f>
+        <v>豆腐肉捲</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="E125" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A126" s="21" t="str">
+        <f>_xlfn.XLOOKUP(B126,表格1[ID],表格1[Dish])</f>
+        <v>豆腐肉捲</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="E126" s="1">
+        <v>1</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+      <c r="A127" s="21" t="str">
+        <f>_xlfn.XLOOKUP(B127,表格1[ID],表格1[Dish])</f>
+        <v>豆腐肉捲</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E127" s="1">
+        <v>1</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A128" s="21" t="str">
+        <f>_xlfn.XLOOKUP(B128,表格1[ID],表格1[Dish])</f>
+        <v>豆腐肉捲</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="E128" s="1">
+        <v>50</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -17456,7 +18227,7 @@
           <x14:formula1>
             <xm:f>材料庫!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>C1:C1048576</xm:sqref>
+          <xm:sqref>D1:D1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -17466,606 +18237,1632 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4047E3D-8CBE-4470-86D8-478F6834C272}">
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="2" width="8.7265625" style="1"/>
-    <col min="3" max="3" width="97.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.7265625" style="1"/>
+    <col min="1" max="1" width="21.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="8.7265625" style="1"/>
+    <col min="4" max="4" width="97.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="57.54296875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="53.6328125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="56.54296875" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A1" s="23" t="s">
+        <v>873</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="C1" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A2" s="1" t="s">
+      <c r="E1" s="8" t="s">
+        <v>870</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>871</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A2" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B2,表格1[ID],表格1[Dish])</f>
+        <v>椰青木瓜果凍</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B2" s="1">
+      <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A3" s="1" t="s">
+      <c r="E2" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Cut the papaya in half, remove the seeds in the middle, and make a papaya cup</v>
+      </c>
+      <c r="F2" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Hatiin ang papaya sa gitna, alisin ang mga buto sa gitna, at gumawa ng tasa ng papaya</v>
+      </c>
+      <c r="G2" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Belah pepaya menjadi dua, keluarkan biji di tengah, dan buat cangkir pepaya</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A3" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B3,表格1[ID],表格1[Dish])</f>
+        <v>椰青木瓜果凍</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B3" s="1">
+      <c r="C3" s="1">
         <v>2</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A4" s="1" t="s">
+      <c r="E3" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Mix the coconut water, coconut milk, milk, and sugar, add the vegetable powder, cook until the sugar dissolves, then let cool</v>
+      </c>
+      <c r="F3" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Haluin ang tubig ng niyog, gatas ng niyog, gatas, at asukal, idagdag ang pulbos ng gulay, lutuin hanggang matunaw ang asukal, pagkatapos ay palamigin</v>
+      </c>
+      <c r="G3" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Campur air kelapa, santan, susu, dan gula, tambahkan bubuk sayuran, masak sampai gula larut, lalu biarkan dingin</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A4" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B4,表格1[ID],表格1[Dish])</f>
+        <v>椰青木瓜果凍</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B4" s="1">
+      <c r="C4" s="1">
         <v>3</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A5" s="1" t="s">
+      <c r="E4" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Pour into a papaya cup and refrigerate until set</v>
+      </c>
+      <c r="F4" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Ibuhos sa isang tasa ng papaya at ilagay sa refrigerator hanggang tumigas</v>
+      </c>
+      <c r="G4" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Tuang ke dalam cangkir pepaya dan simpan di kulkas hingga mengeras</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A5" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B5,表格1[ID],表格1[Dish])</f>
+        <v>椰青木瓜果凍</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B5" s="1">
+      <c r="C5" s="1">
         <v>4</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A6" s="1" t="s">
+      <c r="E5" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>When eating, just cut it into small pieces</v>
+      </c>
+      <c r="F5" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Kapag kumakain, hiwain lang ito sa maliliit na piraso</v>
+      </c>
+      <c r="G5" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Saat makan, cukup potong menjadi potongan kecil</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A6" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B6,表格1[ID],表格1[Dish])</f>
+        <v>紫薯布甸</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B6" s="1">
+      <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A7" s="1" t="s">
+      <c r="E6" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Steam, peel the purple-fleshed sweet potatoes, and mash them with a knife</v>
+      </c>
+      <c r="F6" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>I-steam, balatan ang mga kamote na may lila na laman, at durugin gamit ang kutsilyo</v>
+      </c>
+      <c r="G6" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Kukus, kupas ubi jalar berisi ungu, lalu tumbuk dengan pisau</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A7" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B7,表格1[ID],表格1[Dish])</f>
+        <v>紫薯布甸</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B7" s="1">
+      <c r="C7" s="1">
         <v>2</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A8" s="1" t="s">
+      <c r="E7" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Add 150ML of milk to the purple sweet potato puree, then put it in a blender and mix well</v>
+      </c>
+      <c r="F7" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Idagdag ang 150ML ng gatas sa purple sweet potato puree, pagkatapos ilagay sa blender at haluin nang mabuti</v>
+      </c>
+      <c r="G7" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Tambahkan 150ML susu ke pure ubi jalar ungu, lalu masukkan ke blender dan aduk rata</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A8" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B8,表格1[ID],表格1[Dish])</f>
+        <v>紫薯布甸</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B8" s="1">
+      <c r="C8" s="1">
         <v>3</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A9" s="1" t="s">
+      <c r="E8" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Put the remaining milk and cream into a pot and heat over low heat, then add sugar and konjac powder, stirring slowly until completely dissolved</v>
+      </c>
+      <c r="F8" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Ilagay ang natitirang gatas at cream sa palayok at painitin sa mababang init, pagkatapos ay magdagdag ng asukal at konjac powder, dahan-dahang haluin hanggang tuluyang matunaw</v>
+      </c>
+      <c r="G8" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Masukkan sisa susu dan krim ke dalam panci dan panaskan dengan api kecil, lalu tambahkan gula dan bubuk konjac, aduk perlahan hingga benar-benar larut</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A9" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B9,表格1[ID],表格1[Dish])</f>
+        <v>紫薯布甸</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B9" s="1">
+      <c r="C9" s="1">
         <v>4</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A10" s="1" t="s">
+      <c r="E9" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>After dissolving, gradually add small amounts into the purple sweet potato puree until evenly combined</v>
+      </c>
+      <c r="F9" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Pagkatapos matunaw, dahan-dahang idagdag ang kaunting dami sa purple sweet potato puree hanggang pantay-pantay ang paghahalo</v>
+      </c>
+      <c r="G9" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Setelah larut, tambahkan sedikit ke dalam puree ubi jalar ungu hingga tercampur rata</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A10" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B10,表格1[ID],表格1[Dish])</f>
+        <v>紫薯布甸</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B10" s="1">
+      <c r="C10" s="1">
         <v>5</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A11" s="1" t="s">
+      <c r="E10" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Finally, pour it into a pudding cup, close the lid, and refrigerate until set</v>
+      </c>
+      <c r="F10" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Sa huli, ibuhos ito sa pudding cup, isara ang takip, at ilagay sa refrigerator hanggang tumigas</v>
+      </c>
+      <c r="G10" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Terakhir, tuangkan ke dalam cangkir puding, tutup tutupnya, dan simpan di kulkas hingga mengeras</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A11" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B11,表格1[ID],表格1[Dish])</f>
+        <v>焗葡汁白菌豆腐飯</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B11" s="1">
+      <c r="C11" s="1">
         <v>1</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>382</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A12" s="1" t="s">
+      <c r="E11" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Cut the tofu into cubes, fry until golden brown, then set aside</v>
+      </c>
+      <c r="F11" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Hiwain ang tofu sa mga cube, igisa hanggang maging golden brown, pagkatapos ay itabi</v>
+      </c>
+      <c r="G11" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Potong tahu menjadi dadu dadu, goreng hingga keemasan, lalu sisihkan</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A12" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B12,表格1[ID],表格1[Dish])</f>
+        <v>焗葡汁白菌豆腐飯</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B12" s="1">
+      <c r="C12" s="1">
         <v>2</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A13" s="1" t="s">
+      <c r="E12" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Heat a wok over medium heat, add butter, and once melted, add turmeric powder and curry powder and stir-fry until fragrant. Add the superior broth, bring to a boil, then add milk and cream, season with salt and sugar</v>
+      </c>
+      <c r="F12" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Painitin ang wok sa katamtamang init, magdagdag ng mantikilya, at kapag natunaw, idagdag ang turmeric powder at curry powder at igisa hanggang mabango. Idagdag ang superior na sabaw, pakuluan, pagkatapos ay magdagdag ng gatas at cream, timplahan ng asin at asukal</v>
+      </c>
+      <c r="G12" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Panaskan wajan di atas api sedang, tambahkan mentega, dan setelah meleleh, tambahkan bubuk kunyit dan bubuk kari lalu tumis hingga harum. Tambahkan kaldu superior, didihkan, lalu tambahkan susu dan krim, bumbui dengan garam dan gula</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A13" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B13,表格1[ID],表格1[Dish])</f>
+        <v>焗葡汁白菌豆腐飯</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B13" s="1">
+      <c r="C13" s="1">
         <v>3</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A14" s="1" t="s">
+      <c r="E13" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Finally, add tofu, slice white mushrooms and coconut milk, then add thickened sauce and cook until thickened</v>
+      </c>
+      <c r="F13" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Sa huli, idagdag ang tofu, hiwain ang puting kabute at gatas ng niyog, pagkatapos ay lagyan ng malapot na sarsa at lutuin hanggang lumapot</v>
+      </c>
+      <c r="G13" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Terakhir, tambahkan tahu, iris jamur putih dan santan, lalu tambahkan saus kental dan masak hingga kental</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A14" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B14,表格1[ID],表格1[Dish])</f>
+        <v>焗葡汁白菌豆腐飯</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B14" s="1">
+      <c r="C14" s="1">
         <v>4</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A15" s="1" t="s">
+      <c r="E14" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Place the white rice on a baking dish, then pour the cooked tofu over the rice surface and sprinkle some cheese</v>
+      </c>
+      <c r="F14" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Ilagay ang puting kanin sa isang baking dish, pagkatapos ibuhos ang nilutong tofu sa ibabaw ng kanin at budburan ng kaunting keso</v>
+      </c>
+      <c r="G14" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Letakkan nasi putih di atas loyang, lalu tuangkan tahu yang sudah matang di atas permukaan nasi dan taburi sedikit keju</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A15" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B15,表格1[ID],表格1[Dish])</f>
+        <v>焗葡汁白菌豆腐飯</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B15" s="1">
+      <c r="C15" s="1">
         <v>5</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A16" s="1" t="s">
+      <c r="E15" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Preheat the oven to 200°C and bake for about 5-8 minutes to finish</v>
+      </c>
+      <c r="F15" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Painitin ang oven sa 200°C at i-bake ng mga 5-8 minuto para matapos</v>
+      </c>
+      <c r="G15" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Panaskan oven pada suhu 200°C dan panggang selama sekitar 5-8 menit untuk selesai</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A16" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B16,表格1[ID],表格1[Dish])</f>
+        <v>素羅宋湯</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B16" s="1">
+      <c r="C16" s="1">
         <v>1</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A17" s="1" t="s">
+      <c r="E16" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>After boiling water, add the diced potatoes, diced carrots, peeled and diced tomatoes, and simmer over medium heat</v>
+      </c>
+      <c r="F16" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Pagkatapos pakuluan ang tubig, idagdag ang diced na patatas, diced carrots, balatan at diced na kamatis, at pakuluan sa katamtamang init</v>
+      </c>
+      <c r="G16" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Setelah air direbus, tambahkan kentang dadu, wortel dadu, tomat yang dikupas dan dipotong dadu, lalu didihkan dengan api sedang</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A17" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B17,表格1[ID],表格1[Dish])</f>
+        <v>素羅宋湯</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B17" s="1">
+      <c r="C17" s="1">
         <v>2</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="D17" s="1" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A18" s="1" t="s">
+      <c r="E17" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Melt beef fat in a skillet, add thinly sliced mushrooms, and stir-fry until cooked</v>
+      </c>
+      <c r="F17" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Tunawin ang taba ng baka sa kawali, idagdag ang manipis na hiniwang kabute, at igisa hanggang maluto</v>
+      </c>
+      <c r="G17" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Lelehkan lemak sapi di wajan, tambahkan jamur iris tipis, dan tumis sampai matang</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A18" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B18,表格1[ID],表格1[Dish])</f>
+        <v>素羅宋湯</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B18" s="1">
+      <c r="C18" s="1">
         <v>3</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A19" s="1" t="s">
+      <c r="E18" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Put the cooked mushrooms into the soup pot</v>
+      </c>
+      <c r="F18" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Ilagay ang nilutong kabute sa palayok ng sopas</v>
+      </c>
+      <c r="G18" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Masukkan jamur yang sudah matang ke dalam panci sup</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A19" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B19,表格1[ID],表格1[Dish])</f>
+        <v>素羅宋湯</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B19" s="1">
+      <c r="C19" s="1">
         <v>4</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>372</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A20" s="1" t="s">
+      <c r="E19" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Add cabbage, tomato paste, and superior broth. Bring to a boil over medium heat, then simmer on low for 50 minutes. After cooking, add sugar and pepper before serving</v>
+      </c>
+      <c r="F19" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Idagdag ang repolyo, tomato paste, at superior broth. Pakuluan sa katamtamang init, pagkatapos ay pakuluan sa mababang init ng 50 minuto. Pagkatapos lutuin, magdagdag ng asukal at paminta bago ihain</v>
+      </c>
+      <c r="G19" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Tambahkan kubis, pasta tomat, dan kaldu superior. Didihkan dengan api sedang, lalu didihkan dengan api kecil selama 50 menit. Setelah memasak, tambahkan gula dan lada sebelum disajikan</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A20" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B20,表格1[ID],表格1[Dish])</f>
+        <v>薯仔沙律蛋包</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B20" s="1">
+      <c r="C20" s="1">
         <v>1</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A21" s="1" t="s">
+      <c r="E20" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>After boiling the eggs, chop them. Blanch the broccoli and carrot, then add a little salt and mix the sauce well</v>
+      </c>
+      <c r="F20" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Pagkatapos pakuluan ang mga itlog, tadtarin ang mga ito. I-blanch ang broccoli at karot, pagkatapos ay magdagdag ng kaunting asin at haluin nang mabuti ang sarsa</v>
+      </c>
+      <c r="G20" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Setelah telur direbus, cincang. Rebus brokoli dan wortel, lalu tambahkan sedikit garam dan aduk saus rata</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A21" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B21,表格1[ID],表格1[Dish])</f>
+        <v>薯仔沙律蛋包</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B21" s="1">
+      <c r="C21" s="1">
         <v>2</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>374</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A22" s="1" t="s">
+      <c r="E21" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Peel and slice the potatoes thinly, steam until cooked, mash, then add chopped egg, broccoli, carrot, and sauce</v>
+      </c>
+      <c r="F21" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Balatan at hiwain nang manipis ang patatas, i-steam hanggang maluto, durugin, pagkatapos ay idagdag ang tinadtad na itlog, broccoli, karot, at sarsa</v>
+      </c>
+      <c r="G21" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Kupas dan iris tipis kentang, kukus sampai matang, tumbukkan, lalu tambahkan telur cincang, brokoli, wortel, dan saus</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A22" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B22,表格1[ID],表格1[Dish])</f>
+        <v>薯仔沙律蛋包</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B22" s="1">
+      <c r="C22" s="1">
         <v>3</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A23" s="1" t="s">
+      <c r="E22" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Place it in a pre-cut dinner bag to finish</v>
+      </c>
+      <c r="F22" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Ilagay ito sa pre-cut na dinner bag para tapusin</v>
+      </c>
+      <c r="G22" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Masukkan ke dalam kantong makan malam yang sudah dipotong untuk menyelesaikan</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B23,表格1[ID],表格1[Dish])</f>
+        <v>麻婆豆腐</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B23" s="1">
+      <c r="C23" s="1">
         <v>1</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="D23" s="10" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A24" s="1" t="s">
+      <c r="E23" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Blanch the tofu in boiling water for 1 minute to remove the flavor.</v>
+      </c>
+      <c r="F23" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>I-blanch ang tofu sa kumukulong tubig ng 1 minuto para mawala ang lasa.</v>
+      </c>
+      <c r="G23" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Rebus tahu dalam air mendidih selama 1 menit untuk menghilangkan rasa.</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A24" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B24,表格1[ID],表格1[Dish])</f>
+        <v>麻婆豆腐</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B24" s="1">
+      <c r="C24" s="1">
         <v>2</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="D24" s="10" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A25" s="1" t="s">
+      <c r="E24" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Heat a wok over medium heat, add oil and stir-fry the pork for 1 minute, then add black pepper.</v>
+      </c>
+      <c r="F24" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Painitin ang wok sa katamtamang init, idagdag ang mantika at igisa ang baboy ng 1 minuto, pagkatapos ay idagdag ang itim na paminta.</v>
+      </c>
+      <c r="G24" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Panaskan wajan dengan api sedang, tambahkan minyak dan tumis daging babi selama 1 menit, lalu tambahkan lada hitam.</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A25" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B25,表格1[ID],表格1[Dish])</f>
+        <v>麻婆豆腐</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B25" s="1">
+      <c r="C25" s="1">
         <v>3</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="D25" s="10" t="s">
         <v>371</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A26" s="1" t="s">
+      <c r="E25" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Remove the meat and set aside. Leave some oil, add Sichuan peppercorn oil and spicy doubanjiang, then add minced ginger and garlic.</v>
+      </c>
+      <c r="F25" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Alisin ang karne at itabi sa tabi. Mag-iwan ng kaunting mantika, idagdag ang Sichuan peppercorn oil at maanghang na doubanjiang, pagkatapos ay idagdag ang tinadtad na luya at bawang.</v>
+      </c>
+      <c r="G25" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Keluarkan daging dan sisihkan. Sisakan sedikit minyak, tambahkan minyak lada Sichuan dan doubanjiang pedas, lalu tambahkan jahe cincang dan bawang putih.</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A26" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B26,表格1[ID],表格1[Dish])</f>
+        <v>麻婆豆腐</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B26" s="1">
+      <c r="C26" s="1">
         <v>4</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="D26" s="10" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A27" s="1" t="s">
+      <c r="E26" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Add fermented black beans, then add the meat and pickled mustard greens, stir-fry briefly.</v>
+      </c>
+      <c r="F26" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Idagdag ang fermented na black beans, pagkatapos ay idagdag ang karne at pickled mustard greens, at igisa sandali.</v>
+      </c>
+      <c r="G26" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Tambahkan kacang hitam fermentasi, lalu tambahkan daging dan daun mustard acar, tumis sebentar.</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A27" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B27,表格1[ID],表格1[Dish])</f>
+        <v>麻婆豆腐</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B27" s="1">
+      <c r="C27" s="1">
         <v>5</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="D27" s="1" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A28" s="1" t="s">
+      <c r="E27" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Add soup.</v>
+      </c>
+      <c r="F27" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Magdagdag ng sopas.</v>
+      </c>
+      <c r="G27" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Tambahkan sup.</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A28" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B28,表格1[ID],表格1[Dish])</f>
+        <v>麻婆豆腐</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B28" s="1">
+      <c r="C28" s="1">
         <v>6</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="D28" s="10" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A29" s="1" t="s">
+      <c r="E28" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Add dark soy sauce, add the tofu, and simmer on low heat for 3 minutes.</v>
+      </c>
+      <c r="F28" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Idagdag ang madilim na toyo, ilagay ang tofu, at pakuluan sa mababang init ng 3 minuto.</v>
+      </c>
+      <c r="G28" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Tambahkan kecap asin gelap, tambahkan tahu, dan didihkan dengan api kecil selama 3 menit.</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A29" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B29,表格1[ID],表格1[Dish])</f>
+        <v>麻婆豆腐</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B29" s="1">
-        <v>7</v>
-      </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="1">
+        <v>7</v>
+      </c>
+      <c r="D29" s="10" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A30" s="1" t="s">
+      <c r="E29" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Add cornstarch water, add chopped scallions, cook for 30 seconds, and half a teaspoon of sesame oil.</v>
+      </c>
+      <c r="F29" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Magdagdag ng cornstarch water, idagdag ang tinadtad na scallions, lutuin ng 30 segundo, at kalahating kutsarita ng sesame oil.</v>
+      </c>
+      <c r="G29" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Tambahkan air tepung jagung, tambahkan daun bawang cincang, masak selama 30 detik, dan setengah sendok teh minyak wijen.</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A30" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B30,表格1[ID],表格1[Dish])</f>
+        <v>蒜蓉蒸茄子</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B30" s="1">
+      <c r="C30" s="1">
         <v>1</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="D30" s="10" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A31" s="1" t="s">
+      <c r="E30" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Cut open and wash the eggplant, then lay it out on a plate.</v>
+      </c>
+      <c r="F30" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Putulin at hugasan ang talong, pagkatapos ay ilatag ito sa plato.</v>
+      </c>
+      <c r="G30" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Potong dan cuci terong, lalu letakkan di atas piring.</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B31,表格1[ID],表格1[Dish])</f>
+        <v>蒜蓉蒸茄子</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B31" s="1">
+      <c r="C31" s="1">
         <v>2</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="D31" s="10" t="s">
         <v>412</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A32" s="1" t="s">
+      <c r="E31" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Add sugar, cornstarch, and chicken powder to the minced garlic, then mix well.</v>
+      </c>
+      <c r="F31" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Idagdag ang asukal, cornstarch, at chicken powder sa tinadtad na bawang, pagkatapos ay haluin nang mabuti.</v>
+      </c>
+      <c r="G31" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Tambahkan gula, tepung jagung, dan bubuk ayam ke bawang putih cincang, lalu aduk rata.</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B32,表格1[ID],表格1[Dish])</f>
+        <v>蒜蓉蒸茄子</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B32" s="1">
+      <c r="C32" s="1">
         <v>3</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="D32" s="10" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A33" s="1" t="s">
+      <c r="E32" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Heat oil, pour in the minced garlic, mix well, and spread it over the eggplant.</v>
+      </c>
+      <c r="F32" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Painitin ang mantika, ibuhos ang tinadtad na bawang, haluin nang mabuti, at ikalat ito sa talong.</v>
+      </c>
+      <c r="G32" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Panaskan minyak, tuangkan bawang putih cincang, aduk rata, lalu oleskan di atas terong.</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A33" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B33,表格1[ID],表格1[Dish])</f>
+        <v>蒜蓉蒸茄子</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B33" s="1">
+      <c r="C33" s="1">
         <v>4</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="D33" s="10" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A34" s="1" t="s">
+      <c r="E33" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Once the water boils, steam on high heat for 10 minutes.</v>
+      </c>
+      <c r="F33" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Kapag kumulo na ang tubig, i-steam sa mataas na init ng 10 minuto.</v>
+      </c>
+      <c r="G33" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Setelah air mendidih, kukus dengan api tinggi selama 10 menit.</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A34" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B34,表格1[ID],表格1[Dish])</f>
+        <v>蒜蓉蒸茄子</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B34" s="1">
+      <c r="C34" s="1">
         <v>5</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="D34" s="10" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A35" s="1" t="s">
+      <c r="E34" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Add chopped scallions, pour in flaky oil, and pour in hot oil to finish.</v>
+      </c>
+      <c r="F34" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Idagdag ang tinadtad na scallions, ibuhos ang flaky oil, at ibuhos ang mainit na mantika bilang finish.</v>
+      </c>
+      <c r="G34" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Tambahkan daun bawang cincang, tuangkan minyak yang mengelupas, lalu tuangkan minyak panas untuk melengkapi.</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A35" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B35,表格1[ID],表格1[Dish])</f>
+        <v>金銀蛋菠菜</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B35" s="1">
+      <c r="C35" s="1">
         <v>1</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="D35" s="10" t="s">
         <v>423</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A36" s="1" t="s">
+      <c r="E35" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Separate the salted egg whites and yolks; Peel the century eggs and cut into small pieces.</v>
+      </c>
+      <c r="F35" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Paghiwalayin ang maalat na puti ng itlog at pula ng itlog; Balatan ang century eggs at hiwain sa maliliit na piraso.</v>
+      </c>
+      <c r="G35" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Pisahkan putih telur dan kuning telur yang diasinkan; Kupas telur abad dan potong menjadi potongan kecil.</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A36" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B36,表格1[ID],表格1[Dish])</f>
+        <v>金銀蛋菠菜</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B36" s="1">
+      <c r="C36" s="1">
         <v>2</v>
       </c>
-      <c r="C36" s="10" t="s">
+      <c r="D36" s="10" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A37" s="1" t="s">
+      <c r="E36" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Add oil, sauté whole garlic until fragrant, after 1 minute, add spinach and stir-fry quickly, pour in a little chicken broth, and serve with spinach.</v>
+      </c>
+      <c r="F36" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Magdagdag ng mantika, igisa ang buong bawang hanggang mabango, pagkatapos ng 1 minuto, idagdag ang spinach at igisa nang mabilis, ibuhos ang kaunting sabaw ng manok, at ihain kasama ang spinach.</v>
+      </c>
+      <c r="G36" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Tambahkan minyak, tumis bawang putih utuh hingga harum, setelah 1 menit, tambahkan bayam dan tumis dengan cepat, tuang sedikit kaldu ayam, dan sajikan bersama bayam.</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A37" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B37,表格1[ID],表格1[Dish])</f>
+        <v>金銀蛋菠菜</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B37" s="1">
+      <c r="C37" s="1">
         <v>3</v>
       </c>
-      <c r="C37" s="10" t="s">
+      <c r="D37" s="10" t="s">
         <v>456</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A38" s="1" t="s">
+      <c r="E37" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Bring a clear wok to a boil, add chicken broth, first add salted egg yolk and century egg, cook for 2 minutes, then add salted egg whites and beat into egg drops. Add spinach and serve with soup</v>
+      </c>
+      <c r="F37" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Pakuluan ang malinaw na wok, idagdag ang sabaw ng manok, una idagdag ang maalat na pula ng itlog at century egg, lutuin ng 2 minuto, pagkatapos ay idagdag ang maalat na puti ng itlog at batiin hanggang maging egg drops. Idagdag ang spinach at ihain kasama ng sopas</v>
+      </c>
+      <c r="G37" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Didihkan wajan bening, tambahkan kaldu ayam, tambahkan kuning telur asin dan telur abad terlebih dahulu, masak selama 2 menit, lalu tambahkan putih telur asin dan kocok menjadi tetesan telur. Tambahkan bayam dan sajikan bersama sup</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A38" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B38,表格1[ID],表格1[Dish])</f>
+        <v>薑葱焗桶蠔</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B38" s="1">
+      <c r="C38" s="1">
         <v>1</v>
       </c>
-      <c r="C38" s="10" t="s">
+      <c r="D38" s="10" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A39" s="1" t="s">
+      <c r="E38" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Cut the scallion into sections (separate the white and green parts), and slice the ginger for later use.</v>
+      </c>
+      <c r="F38" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Hiwain ang scallion sa mga bahagi (paghiwalayin ang puti at berdeng bahagi), at hiwain ang luya para magamit sa susunod.</v>
+      </c>
+      <c r="G38" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Potong daun bawang menjadi beberapa bagian (pisahkan bagian putih dan hijau), lalu iris jahe untuk digunakan nanti.</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A39" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B39,表格1[ID],表格1[Dish])</f>
+        <v>薑葱焗桶蠔</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B39" s="1">
+      <c r="C39" s="1">
         <v>2</v>
       </c>
-      <c r="C39" s="11" t="s">
+      <c r="D39" s="11" t="s">
         <v>459</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A40" s="1" t="s">
+      <c r="E39" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Rinse the oysters gently with 2 tablespoons of cornstarch until they are no longer cloudy. Absorb the water. Gently wipe off the surface with your hands</v>
+      </c>
+      <c r="F39" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Banlawan nang dahan-dahan ang talaba gamit ang 2 kutsara ng cornstarch hanggang hindi na ito malabo. Sipsipin ang tubig. Dahan-dahang punasan ang ibabaw gamit ang iyong mga kamay</v>
+      </c>
+      <c r="G39" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Bilas tiram dengan lembut menggunakan 2 sendok makan tepung maizena hingga tidak keruh lagi. Serap airnya. Lap permukaannya dengan tangan dengan lembut</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A40" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B40,表格1[ID],表格1[Dish])</f>
+        <v>薑葱焗桶蠔</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B40" s="1">
+      <c r="C40" s="1">
         <v>3</v>
       </c>
-      <c r="C40" s="11" t="s">
+      <c r="D40" s="11" t="s">
         <v>460</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" ht="34" x14ac:dyDescent="0.4">
-      <c r="A41" s="1" t="s">
+      <c r="E40" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>After boiling water, add a little ginger slices, blanch the oysters for 1 minute, remove and dry them, then coat with 3 tablespoons of cornstarch and salt.</v>
+      </c>
+      <c r="F40" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Pagkatapos kumukulo ng tubig, magdagdag ng kaunting hiwa ng luya, i-blanch ang mga talaba ng 1 minuto, alisin at patuyuin, pagkatapos ay balutin ng 3 kutsara ng cornstarch at asin.</v>
+      </c>
+      <c r="G40" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Setelah air direbus, tambahkan sedikit irisan jahe, rebus tiram selama 1 menit, angkat dan keringkan, lalu lapisi dengan 3 sendok makan tepung maizena dan garam.</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="34" x14ac:dyDescent="0.4">
+      <c r="A41" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B41,表格1[ID],表格1[Dish])</f>
+        <v>薑葱焗桶蠔</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B41" s="1">
+      <c r="C41" s="1">
         <v>4</v>
       </c>
-      <c r="C41" s="11" t="s">
+      <c r="D41" s="11" t="s">
         <v>466</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" ht="32.5" x14ac:dyDescent="0.4">
-      <c r="A42" s="1" t="s">
+      <c r="E41" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Heat oil in a pan over medium heat, add ginger slices and scallion whites to release flavor, then remove the ginger and scallion whites, add oysters and pan-fry until slightly golden, then remove. Fry on high heat for 30 seconds and flip to the other side</v>
+      </c>
+      <c r="F41" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Painitin ang mantika sa kawali sa katamtamang init, idagdag ang mga hiwa ng luya at puti ng scallion para mailabas ang lasa, pagkatapos alisin ang luya at puti ng scallion, idagdag ang talaba at iprito sa kawali hanggang bahagyang maging ginto, pagkatapos ay alisin. Iprito sa mataas na init ng 30 segundo at baliktarin sa kabilang gilid</v>
+      </c>
+      <c r="G41" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Panaskan minyak dalam wajan dengan api sedang, tambahkan irisan jahe dan putih bawang bawang untuk melepaskan rasa, lalu keluarkan jahe dan putih daun bawang, tambahkan tiram dan goreng sampai sedikit keemasan, lalu angkat. Goreng dengan api tinggi selama 30 detik lalu balik ke sisi lain</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="32.5" x14ac:dyDescent="0.4">
+      <c r="A42" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B42,表格1[ID],表格1[Dish])</f>
+        <v>薑葱焗桶蠔</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B42" s="1">
+      <c r="C42" s="1">
         <v>5</v>
       </c>
-      <c r="C42" s="11" t="s">
+      <c r="D42" s="11" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A43" s="1" t="s">
+      <c r="E42" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Add garlic and stir-fry until fragrant, then add Shaoxing wine and the scallion and ginger that have just released the flavor. Once fragrant, add the oysters and stir-fry quickly. Divide the sauce in stages to reduce the sauce, then add the green scallions and stir-fry at the same time. Add two drops of sesame oil before serving</v>
+      </c>
+      <c r="F42" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Idagdag ang bawang at igisa hanggang mabango, pagkatapos ay idagdag ang Shaoxing wine at ang scallion at luya na kakalabas lang ng lasa. Kapag mabango, idagdag ang talaba at mabilis na igisa. Hatiin ang sarsa sa mga yugto upang mabawasan ang sarsa, pagkatapos idagdag ang berdeng sibuyas at iprito nang sabay. Magdagdag ng dalawang patak ng sesame oil bago ihain</v>
+      </c>
+      <c r="G42" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Tambahkan bawang putih dan tumis sampai harum, lalu tambahkan Shaoxing wine serta daun bawang dan jahe yang baru saja melepaskan rasa. Setelah harum, tambahkan tiram dan tumis dengan cepat. Bagi saus secara bertahap untuk mengurangi saus, lalu tambahkan daun bawang hijau dan tumis secara bersamaan. Tambahkan dua tetes minyak wijen sebelum disajikan</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A43" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B43,表格1[ID],表格1[Dish])</f>
+        <v>土匪雞翼</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B43" s="1">
+      <c r="C43" s="1">
         <v>1</v>
       </c>
-      <c r="C43" s="10" t="s">
+      <c r="D43" s="10" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A44" s="1" t="s">
+      <c r="E43" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Wash the chicken wings, wipe them dry, and marinate them with seasonings for a few hours</v>
+      </c>
+      <c r="F43" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Hugasan ang mga pakpak ng manok, punasan ito para matuyo, at i-marinate gamit ang mga pampalasa ng ilang oras</v>
+      </c>
+      <c r="G43" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Cuci sayap ayam, lap kering, dan marinasi dengan bumbu selama beberapa jam</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A44" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B44,表格1[ID],表格1[Dish])</f>
+        <v>土匪雞翼</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B44" s="1">
+      <c r="C44" s="1">
         <v>2</v>
       </c>
-      <c r="C44" s="10" t="s">
+      <c r="D44" s="10" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A45" s="1" t="s">
+      <c r="E44" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Place the chicken wings in the air fryer basket, brushing a little oil on the surface.</v>
+      </c>
+      <c r="F44" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Ilagay ang mga pakpak ng manok sa basket ng air fryer, pahiran ng kaunting mantika sa ibabaw.</v>
+      </c>
+      <c r="G44" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Letakkan sayap ayam di keranjang air fryer, oleskan sedikit minyak di permukaannya.</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A45" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B45,表格1[ID],表格1[Dish])</f>
+        <v>土匪雞翼</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B45" s="1">
+      <c r="C45" s="1">
         <v>3</v>
       </c>
-      <c r="C45" s="12" t="s">
+      <c r="D45" s="12" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A46" s="1" t="s">
+      <c r="E45" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Fry at 180°C for about 10 minutes</v>
+      </c>
+      <c r="F45" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Iprito sa 180°C ng mga 10 minuto</v>
+      </c>
+      <c r="G45" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Goreng pada suhu 180°C selama sekitar 10 menit</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A46" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B46,表格1[ID],表格1[Dish])</f>
+        <v>土匪雞翼</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B46" s="1">
+      <c r="C46" s="1">
         <v>4</v>
       </c>
-      <c r="C46" s="10" t="s">
+      <c r="D46" s="10" t="s">
         <v>451</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" ht="34" x14ac:dyDescent="0.4">
-      <c r="A47" s="1" t="s">
+      <c r="E46" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Turn on the air fryer and flip the chicken wings</v>
+      </c>
+      <c r="F46" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Buksan ang air fryer at baliktarin ang mga pakpak ng manok</v>
+      </c>
+      <c r="G46" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Nyalakan air fryer dan balikkan sayap ayam</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="34" x14ac:dyDescent="0.4">
+      <c r="A47" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B47,表格1[ID],表格1[Dish])</f>
+        <v>土匪雞翼</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B47" s="1">
+      <c r="C47" s="1">
         <v>5</v>
       </c>
-      <c r="C47" s="10" t="s">
+      <c r="D47" s="10" t="s">
         <v>457</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A48" s="1" t="s">
+      <c r="E47" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Sprinkle a layer of cumin powder and black/white sesame seeds on top, then air fry at 180°C (or raise to 200°C to release fat) for another 3 to 5 minutes until the chicken skin is golden and crispy, then remove from heat</v>
+      </c>
+      <c r="F47" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Budburan ng patong ng cumin powder at itim/puting linga sa ibabaw, pagkatapos ay i-air fry sa 180°C (o itaas sa 200°C para mawala ang taba) ng isa pang 3 hanggang 5 minuto hanggang maging ginto at malutong ang balat ng manok, pagkatapos ay alisin sa apoy</v>
+      </c>
+      <c r="G47" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Taburkan lapisan bubuk jintan dan biji wijen hitam/putih di atasnya, lalu goreng dengan udara pada suhu 180°C (atau tingkatkan hingga 200°C untuk melepaskan lemak) selama 3 hingga 5 menit lagi hingga kulit ayam berwarna keemasan dan renyah, lalu angkat dari api</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A48" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B48,表格1[ID],表格1[Dish])</f>
+        <v>涼伴雲耳</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B48" s="1">
+      <c r="C48" s="1">
         <v>1</v>
       </c>
-      <c r="C48" s="10" t="s">
+      <c r="D48" s="10" t="s">
         <v>469</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A49" s="1" t="s">
+      <c r="E48" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Soak the black fungus for 30 minutes, drain, and remove sand.</v>
+      </c>
+      <c r="F48" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Ibabad ang itim na fungus ng 30 minuto, i-drain, at alisin ang buhangin.</v>
+      </c>
+      <c r="G48" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Rendam jamur hitam selama 30 menit, tiriskan, dan angkat pasir.</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A49" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B49,表格1[ID],表格1[Dish])</f>
+        <v>涼伴雲耳</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B49" s="1">
+      <c r="C49" s="1">
         <v>2</v>
       </c>
-      <c r="C49" s="10" t="s">
+      <c r="D49" s="10" t="s">
         <v>470</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A50" s="1" t="s">
+      <c r="E49" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Repeat the wash 3 times.</v>
+      </c>
+      <c r="F49" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Ulitin ang paghuhugas ng 3 beses.</v>
+      </c>
+      <c r="G49" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Ulangi pencucian 3 kali.</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A50" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B50,表格1[ID],表格1[Dish])</f>
+        <v>涼伴雲耳</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B50" s="1">
+      <c r="C50" s="1">
         <v>3</v>
       </c>
-      <c r="C50" s="10" t="s">
+      <c r="D50" s="10" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A51" s="1" t="s">
+      <c r="E50" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Add the black fungus to the ice in cold water, boil for 2 minutes, then rinse with cold boiling water.</v>
+      </c>
+      <c r="F50" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Idagdag ang itim na fungus sa yelo sa malamig na tubig, pakuluan ng 2 minuto, pagkatapos banlawan gamit ang malamig na kumukulong tubig.</v>
+      </c>
+      <c r="G50" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Tambahkan jamur hitam ke dalam es dalam air dingin, didihkan selama 2 menit, lalu bilas dengan air mendidih dingin.</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A51" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B51,表格1[ID],表格1[Dish])</f>
+        <v>涼伴雲耳</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B51" s="1">
+      <c r="C51" s="1">
         <v>4</v>
       </c>
-      <c r="C51" s="10" t="s">
+      <c r="D51" s="10" t="s">
         <v>472</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A52" s="1" t="s">
+      <c r="E51" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Drain and mix to season. Store in the refrigerator</v>
+      </c>
+      <c r="F51" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>I-drain at haluin para sa season. Itago sa refrigerator</v>
+      </c>
+      <c r="G51" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Tiriskan dan aduk sesuai bumbu. Simpan di kulkas</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A52" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B52,表格1[ID],表格1[Dish])</f>
+        <v>醬燒豆腐</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="B52" s="1">
+      <c r="C52" s="1">
         <v>1</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="D52" s="5" t="s">
         <v>705</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A53" s="1" t="s">
+      <c r="E52" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Cut the tofu into 8 slices and set aside</v>
+      </c>
+      <c r="F52" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Hiwain ang tofu sa 8 hiwa at itabi</v>
+      </c>
+      <c r="G52" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Potong tahu menjadi 8 iris dan sisihkan</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A53" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B53,表格1[ID],表格1[Dish])</f>
+        <v>醬燒豆腐</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="B53" s="1">
+      <c r="C53" s="1">
         <v>2</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="D53" s="2" t="s">
         <v>706</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A54" s="1" t="s">
+      <c r="E53" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Heat a small amount of oil in a pan, then add the egg and tofu, and pan-fry over medium heat until both sides are golden brown</v>
+      </c>
+      <c r="F53" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Painitin ang kaunting mantika sa kawali, pagkatapos idagdag ang itlog at tofu, at iprito sa katamtamang init hanggang maging gintong kayumanggi ang magkabilang panig</v>
+      </c>
+      <c r="G53" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Panaskan sedikit minyak di wajan, lalu tambahkan telur dan tahu, lalu goreng di atas api sedang hingga kedua sisinya berwarna cokelat keemasan</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A54" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B54,表格1[ID],表格1[Dish])</f>
+        <v>醬燒豆腐</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="B54" s="1">
+      <c r="C54" s="1">
         <v>3</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="D54" s="2" t="s">
         <v>707</v>
+      </c>
+      <c r="E54" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Take a small piece of napkin, hold it with chopsticks, absorb excess oil from the pan, then add the seasonings. Once the tofu absorbs the sauce, it's ready</v>
+      </c>
+      <c r="F54" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Kumuha ng maliit na piraso ng napkin, hawakan gamit ang chopsticks, sipsipin ang sobrang mantika mula sa kawali, tapos idagdag ang mga pampalasa. Kapag na-absorb na ng tofu ang sarsa, handa na ito</v>
+      </c>
+      <c r="G54" s="1" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Ambil sepotong kecil serbet, pegang dengan sumpit, serap minyak berlebih dari wajan, lalu tambahkan bumbu. Setelah tahu menyerap saus, sudah siap</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A55" s="22" t="str">
+        <f>_xlfn.XLOOKUP(B55,表格1[ID],表格1[Dish])</f>
+        <v>蒜香蒸豬五花高麗菜</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="C55" s="1">
+        <v>1</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="E55" s="21" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Arrange the cabbage and pork belly slices evenly in the pan, then drizzle with Shaoxing wine (optional).</v>
+      </c>
+      <c r="F55" s="21" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Ayusin nang pantay-pantay ang hiwa ng repolyo at pork belly sa kawali, pagkatapos ay ibuhos ng Shaoxing wine (opsyonal).</v>
+      </c>
+      <c r="G55" s="21" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Susun irisan kubis dan perut babi secara merata di wajan, lalu siram dengan anggur Shaoxing (opsional).</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A56" s="21" t="str">
+        <f>_xlfn.XLOOKUP(B56,表格1[ID],表格1[Dish])</f>
+        <v>蒜香蒸豬五花高麗菜</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="C56" s="1">
+        <v>2</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="E56" s="21" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Cover the pot and simmer over low heat for 7-10 minutes until the meat slices are fully cooked</v>
+      </c>
+      <c r="F56" s="21" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Takpan ang kaldero at pakuluan sa mababang init ng 7-10 minuto hanggang luto nang husto ang mga hiwa ng karne</v>
+      </c>
+      <c r="G56" s="21" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Tutup panci dan didihkan dengan api kecil selama 7-10 menit hingga irisan daging benar-benar matang</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A57" s="21" t="str">
+        <f>_xlfn.XLOOKUP(B57,表格1[ID],表格1[Dish])</f>
+        <v>蒜香蒸豬五花高麗菜</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="C57" s="1">
+        <v>3</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="E57" s="21" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Mix the first four seasonings with minced garlic and pour over the meat slices.</v>
+      </c>
+      <c r="F57" s="21" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Haluin ang unang apat na pampalasa sa giniling na bawang at ibuhos sa ibabaw ng mga hiwa ng karne.</v>
+      </c>
+      <c r="G57" s="21" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Campurkan empat bumbu pertama dengan bawang putih cincang dan tuangkan di atas irisan daging.</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A58" s="21" t="str">
+        <f>_xlfn.XLOOKUP(B58,表格1[ID],表格1[Dish])</f>
+        <v>豆腐肉捲</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="C58" s="1">
+        <v>1</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="E58" s="21" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Wrap the tofu strips inside the meat slices and roll them up</v>
+      </c>
+      <c r="F58" s="21" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Balutin ang mga hiwa ng tofu sa loob ng mga hiwa ng karne at i-roll ito</v>
+      </c>
+      <c r="G58" s="21" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Bungkus irisan tahu di dalam irisan daging dan gulung</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A59" s="21" t="str">
+        <f>_xlfn.XLOOKUP(B59,表格1[ID],表格1[Dish])</f>
+        <v>豆腐肉捲</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="C59" s="1">
+        <v>2</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="E59" s="21" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Heat a small amount of oil in the pan, then pan-fry the meat seams facing down over medium-low heat. If you have leftover tofu, you can also add it to the pan to fry together</v>
+      </c>
+      <c r="F59" s="21" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Painitin ang kaunting mantika sa kawali, pagkatapos ay iprito ang mga seam ng karne na nakaharap pababa sa medium-low na init. Kung may natirang tofu, maaari mo rin itong idagdag sa kawali para iprito nang sabay-sabay</v>
+      </c>
+      <c r="G59" s="21" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Panaskan sedikit minyak di wajan, lalu goreng bagian daging menghadap ke bawah dengan api sedang-rendah. Jika Anda punya tahu sisa, Anda juga bisa menambahkannya ke wajan untuk digoreng bersama</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="17" x14ac:dyDescent="0.4">
+      <c r="A60" s="21" t="str">
+        <f>_xlfn.XLOOKUP(B60,表格1[ID],表格1[Dish])</f>
+        <v>豆腐肉捲</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="C60" s="1">
+        <v>3</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="E60" s="21" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","en")</f>
+        <v>Once every side of the meat is cooked, pour the seasonings over it. Stir the meat occasionally to ensure the sauce absorbs evenly. Once the sauce thickens and the meat rolls are colored and flavorful, it's ready</v>
+      </c>
+      <c r="F60" s="21" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","fil")</f>
+        <v>Kapag luto na ang bawat gilid ng karne, ibuhos ang mga pampalasa dito. Haluin paminsan-minsan ang karne para pantay ang pagsipsip ng sarsa. Kapag lumapot na ang sarsa at may kulay at lasa na ang meat rolls, handa na ito</v>
+      </c>
+      <c r="G60" s="21" t="str">
+        <f>_xlfn.TRANSLATE(Steps[[#This Row],[內容]],"zh-cht","id")</f>
+        <v>Setelah setiap sisi daging matang, tuangkan bumbu di atasnya. Aduk daging sesekali agar saus terserap secara merata. Setelah saus mengental dan daging berwarna serta beraroma lezat, saus siap</v>
       </c>
     </row>
   </sheetData>
@@ -18080,7 +19877,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB00F412-7175-4B8C-93B4-B4DD0A4DEA6F}">
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="14.7265625" style="1" bestFit="1" customWidth="1"/>
@@ -18443,9 +20240,9 @@
         <f>_xlfn.TRANSLATE(ingredient_unit[[#This Row],[材料]],"zh-cht","en")</f>
         <v>Cheese</v>
       </c>
-      <c r="C21" s="1" t="e" vm="1">
+      <c r="C21" s="1" t="str">
         <f>_xlfn.TRANSLATE(ingredient_unit[[#This Row],[材料]],"zh-cht","fil")</f>
-        <v>#VALUE!</v>
+        <v>Keso</v>
       </c>
       <c r="D21" s="1" t="str">
         <f>_xlfn.TRANSLATE(ingredient_unit[[#This Row],[材料]],"zh-cht","id")</f>
@@ -19302,6 +21099,49 @@
       <c r="D71" s="1" t="str">
         <f>_xlfn.TRANSLATE(ingredient_unit[[#This Row],[材料]],"zh-cht","id")</f>
         <v>Minyak wijen</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="17" x14ac:dyDescent="0.4">
+      <c r="A72" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="B72" s="1" t="str">
+        <f>_xlfn.TRANSLATE(ingredient_unit[[#This Row],[材料]],"zh-cht","en")</f>
+        <v>Thinly sliced pork shoulder</v>
+      </c>
+      <c r="C72" s="21" t="str">
+        <f>_xlfn.TRANSLATE(ingredient_unit[[#This Row],[材料]],"zh-cht","fil")</f>
+        <v>Manipis na hiniwang balikat ng baboy</v>
+      </c>
+      <c r="D72" s="1" t="str">
+        <f>_xlfn.TRANSLATE(ingredient_unit[[#This Row],[材料]],"zh-cht","id")</f>
+        <v>Bahu babi iris tipis</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="17" x14ac:dyDescent="0.4">
+      <c r="A73" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="C73" s="21" t="str">
+        <f>_xlfn.TRANSLATE(ingredient_unit[[#This Row],[材料]],"zh-cht","fil")</f>
+        <v>Matibay na tofu</v>
+      </c>
+      <c r="D73" s="21" t="str">
+        <f>_xlfn.TRANSLATE(ingredient_unit[[#This Row],[材料]],"zh-cht","id")</f>
+        <v>Tahu padat</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A74" s="24" t="s">
+        <v>884</v>
+      </c>
+      <c r="C74" s="21" t="str">
+        <f>_xlfn.TRANSLATE(ingredient_unit[[#This Row],[材料]],"zh-cht","fil")</f>
+        <v>Mirin</v>
+      </c>
+      <c r="D74" s="21" t="str">
+        <f>_xlfn.TRANSLATE(ingredient_unit[[#This Row],[材料]],"zh-cht","id")</f>
+        <v>mirin</v>
       </c>
     </row>
   </sheetData>
